--- a/data/sample_smart_money_idx.xlsx
+++ b/data/sample_smart_money_idx.xlsx
@@ -610,7 +610,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1885,7 +1885,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2260,7 +2260,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3085,7 +3085,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3535,7 +3535,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3610,7 +3610,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3835,7 +3835,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -4060,7 +4060,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -4885,7 +4885,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -4960,7 +4960,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -5035,7 +5035,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5110,7 +5110,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -5560,7 +5560,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -5635,7 +5635,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -5935,7 +5935,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -6085,7 +6085,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6385,7 +6385,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -6460,7 +6460,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -6610,7 +6610,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -6685,7 +6685,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -6760,7 +6760,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -6835,7 +6835,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -6910,7 +6910,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -6985,7 +6985,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -7135,7 +7135,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -7210,7 +7210,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -7285,7 +7285,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -7510,7 +7510,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -7585,7 +7585,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -7735,7 +7735,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -7885,7 +7885,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8110,7 +8110,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -8185,7 +8185,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8260,7 +8260,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -8560,7 +8560,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -8635,7 +8635,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8710,7 +8710,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -8785,7 +8785,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -8860,7 +8860,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -8935,7 +8935,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9010,7 +9010,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9160,7 +9160,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -9235,7 +9235,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9460,7 +9460,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -9535,7 +9535,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9610,7 +9610,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9760,7 +9760,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -9835,7 +9835,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -9985,7 +9985,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10060,7 +10060,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -10135,7 +10135,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -10285,7 +10285,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10360,7 +10360,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -10435,7 +10435,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10660,7 +10660,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10810,7 +10810,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -11185,7 +11185,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -11335,7 +11335,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -11410,7 +11410,7 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -11560,7 +11560,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -11635,7 +11635,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -11860,7 +11860,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -12010,7 +12010,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -12085,7 +12085,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -12160,7 +12160,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -12310,7 +12310,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -12460,7 +12460,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -12535,7 +12535,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -12610,7 +12610,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -12685,7 +12685,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -12760,7 +12760,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -12835,7 +12835,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -12910,7 +12910,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -13060,7 +13060,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -13210,7 +13210,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -13360,7 +13360,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -13435,7 +13435,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -13510,7 +13510,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -13585,7 +13585,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -13660,7 +13660,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -13735,7 +13735,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -13885,7 +13885,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -13960,7 +13960,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -14185,7 +14185,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -14335,7 +14335,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -14485,7 +14485,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -14560,7 +14560,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -14635,7 +14635,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -14710,7 +14710,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -14785,7 +14785,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -14860,7 +14860,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -15010,7 +15010,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -15085,7 +15085,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -15160,7 +15160,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -15235,7 +15235,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -15310,7 +15310,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -15385,7 +15385,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -15460,7 +15460,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -15535,7 +15535,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -15610,7 +15610,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -15685,7 +15685,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -15760,7 +15760,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -15910,7 +15910,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -15985,7 +15985,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -16060,7 +16060,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -16135,7 +16135,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -16210,7 +16210,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -16285,7 +16285,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -16360,7 +16360,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -16435,7 +16435,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -16510,7 +16510,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -16585,7 +16585,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -16660,7 +16660,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -16735,7 +16735,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -16810,7 +16810,7 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -16885,7 +16885,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -16960,7 +16960,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -17035,7 +17035,7 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
@@ -17185,7 +17185,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -17335,7 +17335,7 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -17410,7 +17410,7 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -17485,7 +17485,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -17560,7 +17560,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -17635,7 +17635,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -17710,7 +17710,7 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -17785,7 +17785,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -17935,7 +17935,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -18010,7 +18010,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -18085,7 +18085,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -18160,7 +18160,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -18235,7 +18235,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -18310,7 +18310,7 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -18385,7 +18385,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -18535,7 +18535,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -18610,7 +18610,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -18760,7 +18760,7 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -18835,7 +18835,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -18910,7 +18910,7 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -18985,7 +18985,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -19135,7 +19135,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -19285,7 +19285,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -19360,7 +19360,7 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -19435,7 +19435,7 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -19510,7 +19510,7 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -19585,7 +19585,7 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -19810,7 +19810,7 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -19885,7 +19885,7 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -19960,7 +19960,7 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -20035,7 +20035,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -20110,7 +20110,7 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -20185,7 +20185,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -20335,7 +20335,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -20410,7 +20410,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -20485,7 +20485,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -20560,7 +20560,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -20635,7 +20635,7 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -20710,7 +20710,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -20785,7 +20785,7 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -20935,7 +20935,7 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -21010,7 +21010,7 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -21085,7 +21085,7 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -21160,7 +21160,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -21235,7 +21235,7 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -21310,7 +21310,7 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -21385,7 +21385,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -21535,7 +21535,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -21610,7 +21610,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -21685,7 +21685,7 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -21760,7 +21760,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -21835,7 +21835,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -21910,7 +21910,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -21985,7 +21985,7 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -22135,7 +22135,7 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -22210,7 +22210,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -22285,7 +22285,7 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -22360,7 +22360,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -22435,7 +22435,7 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -22510,7 +22510,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -22585,7 +22585,7 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -22735,7 +22735,7 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -22810,7 +22810,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -22885,7 +22885,7 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -22960,7 +22960,7 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -23035,7 +23035,7 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -23110,7 +23110,7 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -23185,7 +23185,7 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -23335,7 +23335,7 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -23410,7 +23410,7 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -23485,7 +23485,7 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -23560,7 +23560,7 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -23635,7 +23635,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -23710,7 +23710,7 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -23785,7 +23785,7 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -23935,7 +23935,7 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -24010,7 +24010,7 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -24085,7 +24085,7 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -24160,7 +24160,7 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -24235,7 +24235,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -24385,7 +24385,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -24535,7 +24535,7 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -24610,7 +24610,7 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -24685,7 +24685,7 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -24760,7 +24760,7 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -24835,7 +24835,7 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -24910,7 +24910,7 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
@@ -24985,7 +24985,7 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
@@ -25135,7 +25135,7 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
@@ -25210,7 +25210,7 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
@@ -25285,7 +25285,7 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
@@ -25360,7 +25360,7 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -25510,7 +25510,7 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
@@ -25585,7 +25585,7 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
@@ -25735,7 +25735,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
@@ -25810,7 +25810,7 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
@@ -25885,7 +25885,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
@@ -25960,7 +25960,7 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
@@ -26035,7 +26035,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
@@ -26110,7 +26110,7 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
@@ -26185,7 +26185,7 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
@@ -26335,7 +26335,7 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
@@ -26410,7 +26410,7 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
@@ -26485,7 +26485,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
@@ -26560,7 +26560,7 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
@@ -26635,7 +26635,7 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
@@ -26710,7 +26710,7 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
@@ -26785,7 +26785,7 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
@@ -26935,7 +26935,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
@@ -27010,7 +27010,7 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
@@ -27085,7 +27085,7 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
@@ -27160,7 +27160,7 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
@@ -27235,7 +27235,7 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
@@ -27310,7 +27310,7 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
@@ -27385,7 +27385,7 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
@@ -27535,7 +27535,7 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
@@ -27610,7 +27610,7 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
@@ -27685,7 +27685,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
@@ -27760,7 +27760,7 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
@@ -27835,7 +27835,7 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
@@ -27910,7 +27910,7 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
@@ -27985,7 +27985,7 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
@@ -28135,7 +28135,7 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
@@ -28210,7 +28210,7 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
@@ -28285,7 +28285,7 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
@@ -28360,7 +28360,7 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
@@ -28435,7 +28435,7 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
@@ -28510,7 +28510,7 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
@@ -28585,7 +28585,7 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">

--- a/data/sample_smart_money_idx.xlsx
+++ b/data/sample_smart_money_idx.xlsx
@@ -610,7 +610,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1885,7 +1885,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2260,7 +2260,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3085,7 +3085,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3535,7 +3535,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3610,7 +3610,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3835,7 +3835,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -4060,7 +4060,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -4885,7 +4885,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -4960,7 +4960,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -5035,7 +5035,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5110,7 +5110,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -5560,7 +5560,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -5635,7 +5635,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -5935,7 +5935,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -6085,7 +6085,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6385,7 +6385,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -6460,7 +6460,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -6610,7 +6610,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -6685,7 +6685,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -6760,7 +6760,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -6835,7 +6835,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -6910,7 +6910,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -6985,7 +6985,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -7135,7 +7135,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -7210,7 +7210,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -7285,7 +7285,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -7510,7 +7510,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -7585,7 +7585,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -7735,7 +7735,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -7885,7 +7885,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8110,7 +8110,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -8185,7 +8185,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8260,7 +8260,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -8335,7 +8335,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -8560,7 +8560,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -8635,7 +8635,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8710,7 +8710,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -8785,7 +8785,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -8860,7 +8860,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -8935,7 +8935,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9010,7 +9010,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9160,7 +9160,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -9235,7 +9235,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9460,7 +9460,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -9535,7 +9535,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9610,7 +9610,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9760,7 +9760,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -9835,7 +9835,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -9985,7 +9985,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10060,7 +10060,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -10135,7 +10135,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -10285,7 +10285,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10360,7 +10360,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -10435,7 +10435,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -10585,7 +10585,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10660,7 +10660,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10810,7 +10810,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -11185,7 +11185,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -11335,7 +11335,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -11410,7 +11410,7 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -11560,7 +11560,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -11635,7 +11635,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -11860,7 +11860,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -12010,7 +12010,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -12085,7 +12085,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -12160,7 +12160,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -12310,7 +12310,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -12460,7 +12460,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -12535,7 +12535,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -12610,7 +12610,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -12685,7 +12685,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -12760,7 +12760,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -12835,7 +12835,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -12910,7 +12910,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -13060,7 +13060,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -13210,7 +13210,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -13360,7 +13360,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -13435,7 +13435,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -13510,7 +13510,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -13585,7 +13585,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -13660,7 +13660,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -13735,7 +13735,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -13885,7 +13885,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -13960,7 +13960,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -14035,7 +14035,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -14185,7 +14185,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -14335,7 +14335,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -14485,7 +14485,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -14560,7 +14560,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -14635,7 +14635,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -14710,7 +14710,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -14785,7 +14785,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -14860,7 +14860,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -15010,7 +15010,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -15085,7 +15085,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -15160,7 +15160,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -15235,7 +15235,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -15310,7 +15310,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -15385,7 +15385,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -15460,7 +15460,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -15535,7 +15535,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -15610,7 +15610,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -15685,7 +15685,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -15760,7 +15760,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -15910,7 +15910,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -15985,7 +15985,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -16060,7 +16060,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -16135,7 +16135,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -16210,7 +16210,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -16285,7 +16285,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -16360,7 +16360,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -16435,7 +16435,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -16510,7 +16510,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -16585,7 +16585,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -16660,7 +16660,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -16735,7 +16735,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -16810,7 +16810,7 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -16885,7 +16885,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -16960,7 +16960,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -17035,7 +17035,7 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
@@ -17185,7 +17185,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -17335,7 +17335,7 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -17410,7 +17410,7 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -17485,7 +17485,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -17560,7 +17560,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -17635,7 +17635,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -17710,7 +17710,7 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -17785,7 +17785,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -17935,7 +17935,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -18010,7 +18010,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -18085,7 +18085,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -18160,7 +18160,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -18235,7 +18235,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -18310,7 +18310,7 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -18385,7 +18385,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -18535,7 +18535,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -18610,7 +18610,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -18760,7 +18760,7 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -18835,7 +18835,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -18910,7 +18910,7 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -18985,7 +18985,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -19135,7 +19135,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -19285,7 +19285,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -19360,7 +19360,7 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -19435,7 +19435,7 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -19510,7 +19510,7 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -19585,7 +19585,7 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -19735,7 +19735,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -19810,7 +19810,7 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -19885,7 +19885,7 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -19960,7 +19960,7 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -20035,7 +20035,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -20110,7 +20110,7 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -20185,7 +20185,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -20335,7 +20335,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -20410,7 +20410,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -20485,7 +20485,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -20560,7 +20560,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -20635,7 +20635,7 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -20710,7 +20710,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -20785,7 +20785,7 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -20935,7 +20935,7 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -21010,7 +21010,7 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -21085,7 +21085,7 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -21160,7 +21160,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -21235,7 +21235,7 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -21310,7 +21310,7 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -21385,7 +21385,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -21535,7 +21535,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -21610,7 +21610,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -21685,7 +21685,7 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -21760,7 +21760,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -21835,7 +21835,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -21910,7 +21910,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -21985,7 +21985,7 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -22135,7 +22135,7 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -22210,7 +22210,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -22285,7 +22285,7 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -22360,7 +22360,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -22435,7 +22435,7 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -22510,7 +22510,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -22585,7 +22585,7 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -22735,7 +22735,7 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -22810,7 +22810,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -22885,7 +22885,7 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -22960,7 +22960,7 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -23035,7 +23035,7 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -23110,7 +23110,7 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -23185,7 +23185,7 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -23335,7 +23335,7 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -23410,7 +23410,7 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -23485,7 +23485,7 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -23560,7 +23560,7 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -23635,7 +23635,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -23710,7 +23710,7 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -23785,7 +23785,7 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -23935,7 +23935,7 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -24010,7 +24010,7 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -24085,7 +24085,7 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -24160,7 +24160,7 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -24235,7 +24235,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -24385,7 +24385,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -24535,7 +24535,7 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -24610,7 +24610,7 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -24685,7 +24685,7 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -24760,7 +24760,7 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -24835,7 +24835,7 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -24910,7 +24910,7 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
@@ -24985,7 +24985,7 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
@@ -25135,7 +25135,7 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
@@ -25210,7 +25210,7 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
@@ -25285,7 +25285,7 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
@@ -25360,7 +25360,7 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
@@ -25435,7 +25435,7 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -25510,7 +25510,7 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
@@ -25585,7 +25585,7 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
@@ -25735,7 +25735,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
@@ -25810,7 +25810,7 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
@@ -25885,7 +25885,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
@@ -25960,7 +25960,7 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
@@ -26035,7 +26035,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
@@ -26110,7 +26110,7 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
@@ -26185,7 +26185,7 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
@@ -26335,7 +26335,7 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
@@ -26410,7 +26410,7 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
@@ -26485,7 +26485,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
@@ -26560,7 +26560,7 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
@@ -26635,7 +26635,7 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
@@ -26710,7 +26710,7 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
@@ -26785,7 +26785,7 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
@@ -26935,7 +26935,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
@@ -27010,7 +27010,7 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
@@ -27085,7 +27085,7 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
@@ -27160,7 +27160,7 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
@@ -27235,7 +27235,7 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
@@ -27310,7 +27310,7 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
@@ -27385,7 +27385,7 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
@@ -27535,7 +27535,7 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
@@ -27610,7 +27610,7 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
@@ -27685,7 +27685,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
@@ -27760,7 +27760,7 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
@@ -27835,7 +27835,7 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
@@ -27910,7 +27910,7 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
@@ -27985,7 +27985,7 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
@@ -28135,7 +28135,7 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
@@ -28210,7 +28210,7 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
@@ -28285,7 +28285,7 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
@@ -28360,7 +28360,7 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
@@ -28435,7 +28435,7 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
@@ -28510,7 +28510,7 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
@@ -28585,7 +28585,7 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
